--- a/VerveStacks_ESP/vt_vervestacks_ESP_v1.xlsx
+++ b/VerveStacks_ESP/vt_vervestacks_ESP_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2253AD8-A4B1-4BAB-A73C-FD65DA74F740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{759E3DAF-536D-4A17-A4C9-BAD9CCA716FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CDFCC470-4A43-4FCB-B065-3AE9B8CA7E63}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B0B896D4-49D1-4B2A-B113-C78CF397E43E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2774,7 +2774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F981EC2E-BBAC-4BC2-95E1-7029E06811AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC80FF62-5FAD-4B75-A264-97223D3FF4D0}">
   <dimension ref="B9:T164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2853,19 +2853,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.17299880000000001</v>
+        <v>7.9845600000000017E-2</v>
       </c>
       <c r="F11">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G11">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I11">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J11" t="s">
         <v>27</v>
@@ -2909,19 +2909,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.27506149999999996</v>
+        <v>0.18764025000000001</v>
       </c>
       <c r="F12">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G12">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H12">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I12">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J12" t="s">
         <v>28</v>
@@ -2965,19 +2965,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.17299880000000001</v>
+        <v>7.9845600000000017E-2</v>
       </c>
       <c r="F13">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G13">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I13">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J13" t="s">
         <v>29</v>
@@ -3021,19 +3021,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.17299880000000001</v>
+        <v>7.9845600000000017E-2</v>
       </c>
       <c r="F14">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
@@ -3077,19 +3077,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.27506149999999996</v>
+        <v>0.18764025000000001</v>
       </c>
       <c r="F15">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G15">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H15">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I15">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
@@ -3133,19 +3133,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.178087</v>
+        <v>8.2194000000000003E-2</v>
       </c>
       <c r="F16">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G16">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H16">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I16">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -3189,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.11272320000000002</v>
+        <v>8.4542400000000018E-2</v>
       </c>
       <c r="F17">
         <v>3583</v>
@@ -3245,7 +3245,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -3301,7 +3301,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -3357,7 +3357,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.52272499999999988</v>
+        <v>0.39204374999999997</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -3413,7 +3413,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.49118125000000001</v>
+        <v>0.36838593749999993</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -3469,7 +3469,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -3525,7 +3525,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.49118125000000001</v>
+        <v>0.36838593749999993</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -3581,7 +3581,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -3637,7 +3637,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -3693,7 +3693,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3749,7 +3749,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3805,7 +3805,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3861,7 +3861,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000007</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3917,7 +3917,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3973,7 +3973,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4029,7 +4029,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4085,7 +4085,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4141,7 +4141,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4197,7 +4197,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -4253,7 +4253,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -4309,7 +4309,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -4365,7 +4365,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -4421,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.49118125000000001</v>
+        <v>0.36838593749999993</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -4477,7 +4477,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -4533,7 +4533,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.49118125000000001</v>
+        <v>0.36838593749999993</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -4589,7 +4589,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -4645,7 +4645,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -4701,7 +4701,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4757,7 +4757,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4813,7 +4813,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4869,7 +4869,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4925,7 +4925,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -4981,7 +4981,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5037,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5093,7 +5093,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5149,7 +5149,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -5205,7 +5205,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -5261,7 +5261,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -5317,7 +5317,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000007</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -5373,7 +5373,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -5429,7 +5429,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -5485,7 +5485,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -5541,7 +5541,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -5597,7 +5597,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -5653,7 +5653,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -5709,7 +5709,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.49118125000000001</v>
+        <v>0.36838593749999993</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5765,7 +5765,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5821,7 +5821,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -5877,7 +5877,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -5933,7 +5933,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -5989,7 +5989,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6045,7 +6045,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6101,7 +6101,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6157,7 +6157,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -6213,7 +6213,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -6269,7 +6269,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000009</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -6325,7 +6325,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -6381,7 +6381,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -6437,7 +6437,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.52272499999999988</v>
+        <v>0.39204374999999997</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -6493,7 +6493,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.49118125000000001</v>
+        <v>0.36838593750000004</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -6549,7 +6549,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.48667500000000002</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -6605,7 +6605,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -6661,7 +6661,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6717,7 +6717,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6773,7 +6773,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6829,7 +6829,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.48667500000000002</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6885,7 +6885,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6941,7 +6941,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -6997,7 +6997,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.48667500000000002</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7053,7 +7053,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7109,7 +7109,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.48667500000000002</v>
+        <v>0.36500625000000009</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7165,7 +7165,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7221,7 +7221,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.46865000000000007</v>
+        <v>0.35148750000000006</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7277,7 +7277,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7333,7 +7333,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7389,7 +7389,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7445,7 +7445,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7501,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7557,7 +7557,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7613,7 +7613,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7669,7 +7669,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7725,7 +7725,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7781,7 +7781,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7837,7 +7837,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7893,7 +7893,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7949,7 +7949,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8005,7 +8005,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.48667500000000014</v>
+        <v>0.36500624999999998</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8061,7 +8061,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.27938750000000001</v>
+        <v>0.20954062500000004</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8117,7 +8117,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.27037500000000003</v>
+        <v>0.20278125000000002</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8173,7 +8173,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.27037500000000003</v>
+        <v>0.20278125</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8229,7 +8229,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.27037500000000003</v>
+        <v>0.20278125</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8285,7 +8285,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.25235000000000002</v>
+        <v>0.18926250000000003</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8341,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.25235000000000002</v>
+        <v>0.18926250000000003</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8397,7 +8397,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.25235000000000002</v>
+        <v>0.18926250000000003</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -8453,7 +8453,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.25235000000000002</v>
+        <v>0.18926250000000003</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -8509,7 +8509,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.25235000000000002</v>
+        <v>0.18926250000000003</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -8565,7 +8565,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.28839999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -8621,7 +8621,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.43259999999999998</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -8677,7 +8677,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -8733,7 +8733,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.36951250000000002</v>
+        <v>0.27713437499999999</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -8789,7 +8789,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.36951250000000002</v>
+        <v>0.27713437499999999</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -8845,7 +8845,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -8901,7 +8901,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -8957,7 +8957,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.450625</v>
+        <v>0.33796874999999998</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9013,7 +9013,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.22981874999999999</v>
+        <v>0.17236406249999997</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9069,7 +9069,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.22981874999999999</v>
+        <v>0.17236406249999997</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -9125,7 +9125,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.22981874999999999</v>
+        <v>0.17236406249999997</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -9181,7 +9181,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.22080625000000001</v>
+        <v>0.16560468749999999</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -9237,7 +9237,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.24333750000000001</v>
+        <v>0.18250312500000004</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -9293,7 +9293,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.22981874999999999</v>
+        <v>0.17236406249999997</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -9349,7 +9349,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.22981874999999999</v>
+        <v>0.17236406249999997</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -9405,7 +9405,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -9461,7 +9461,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -9517,7 +9517,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -9573,7 +9573,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -9629,7 +9629,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -9685,7 +9685,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -9720,7 +9720,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -9755,7 +9755,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -9790,7 +9790,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -9825,7 +9825,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.24333750000000001</v>
+        <v>0.18250312499999999</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -9860,7 +9860,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -9895,7 +9895,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.29290625000000003</v>
+        <v>0.2196796875</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -9930,7 +9930,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.306425</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -9965,7 +9965,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.306425</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -10000,7 +10000,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.28389375</v>
+        <v>0.21292031250000001</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -10035,7 +10035,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.29290625000000003</v>
+        <v>0.2196796875</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -10070,7 +10070,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.306425</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -10105,7 +10105,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.306425</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -10140,7 +10140,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -10175,7 +10175,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -10210,7 +10210,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -10245,7 +10245,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -10280,7 +10280,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -10315,7 +10315,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -10350,7 +10350,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -10385,7 +10385,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -10420,7 +10420,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.31543749999999998</v>
+        <v>0.23657812499999997</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -10455,7 +10455,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.27037500000000003</v>
+        <v>0.20278125</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -10490,7 +10490,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.26136249999999994</v>
+        <v>0.19602187499999998</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -10525,7 +10525,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.26136249999999994</v>
+        <v>0.19602187499999998</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -10560,7 +10560,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.28839999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -10595,7 +10595,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.28839999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -10630,7 +10630,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.27037500000000003</v>
+        <v>0.20278125</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -10665,7 +10665,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.26136249999999994</v>
+        <v>0.19602187499999998</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -10700,7 +10700,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.28839999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -10735,7 +10735,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.28839999999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -10770,7 +10770,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.26136249999999994</v>
+        <v>0.19602187499999998</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -10800,7 +10800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6F1F2E-C518-4A5B-8040-E7AD6EB57B00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787129DC-07FC-418D-8423-A8D8FF72ADFC}">
   <dimension ref="B9:T372"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10885,7 +10885,7 @@
         <v>0.03</v>
       </c>
       <c r="G11">
-        <v>0.28840000000000005</v>
+        <v>0.21630000000000005</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -10938,7 +10938,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.309</v>
+        <v>0.23174999999999998</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -10991,7 +10991,7 @@
         <v>0.04</v>
       </c>
       <c r="G13">
-        <v>0.309</v>
+        <v>0.23174999999999998</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -11044,7 +11044,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.309</v>
+        <v>0.23174999999999998</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -11097,7 +11097,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G15">
-        <v>0.309</v>
+        <v>0.23175000000000004</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -11150,7 +11150,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G16">
-        <v>0.3296</v>
+        <v>0.2472</v>
       </c>
       <c r="H16">
         <v>5197.5</v>
@@ -11203,7 +11203,7 @@
         <v>0.747</v>
       </c>
       <c r="G17">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H17">
         <v>3850.0000000000005</v>
@@ -11256,7 +11256,7 @@
         <v>0.05</v>
       </c>
       <c r="G18">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H18">
         <v>5197.5</v>
@@ -11309,7 +11309,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -11362,7 +11362,7 @@
         <v>0.05</v>
       </c>
       <c r="G20">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H20">
         <v>5197.5</v>
@@ -11415,7 +11415,7 @@
         <v>0.05</v>
       </c>
       <c r="G21">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H21">
         <v>5197.5</v>
@@ -11468,7 +11468,7 @@
         <v>0.05</v>
       </c>
       <c r="G22">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H22">
         <v>5197.5</v>
@@ -11521,7 +11521,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.3296</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H23">
         <v>5197.5</v>
@@ -11574,7 +11574,7 @@
         <v>0.05</v>
       </c>
       <c r="G24">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H24">
         <v>5197.5</v>
@@ -11627,7 +11627,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G25">
-        <v>0.29869999999999997</v>
+        <v>0.22402499999999997</v>
       </c>
       <c r="H25">
         <v>4427.5</v>
@@ -11680,7 +11680,7 @@
         <v>0.05</v>
       </c>
       <c r="G26">
-        <v>0.3296</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H26">
         <v>5197.5</v>
@@ -11733,7 +11733,7 @@
         <v>0.83480000000000043</v>
       </c>
       <c r="G27">
-        <v>0.37080000000000002</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H27">
         <v>2200</v>
@@ -11786,7 +11786,7 @@
         <v>0.36</v>
       </c>
       <c r="G28">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H28">
         <v>2200</v>
@@ -11839,7 +11839,7 @@
         <v>0.55620000000000003</v>
       </c>
       <c r="G29">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H29">
         <v>2200</v>
@@ -11892,7 +11892,7 @@
         <v>0.13</v>
       </c>
       <c r="G30">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H30">
         <v>2530</v>
@@ -11945,7 +11945,7 @@
         <v>0.13</v>
       </c>
       <c r="G31">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H31">
         <v>2530</v>
@@ -11998,7 +11998,7 @@
         <v>0.58899999999999997</v>
       </c>
       <c r="G32">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H32">
         <v>2200</v>
@@ -12051,7 +12051,7 @@
         <v>0.35</v>
       </c>
       <c r="G33">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H33">
         <v>2200</v>
@@ -12104,7 +12104,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G34">
-        <v>0.49440000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H34">
         <v>1485.0000000000002</v>
@@ -12157,7 +12157,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G35">
-        <v>0.49439999999999995</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H35">
         <v>1485.0000000000002</v>
@@ -12210,7 +12210,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G36">
-        <v>0.49439999999999995</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="H36">
         <v>1485.0000000000002</v>
@@ -12263,7 +12263,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G37">
-        <v>0.49440000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H37">
         <v>1485.0000000000002</v>
@@ -12316,7 +12316,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G38">
-        <v>0.49439999999999995</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="H38">
         <v>1485.0000000000002</v>
@@ -12369,7 +12369,7 @@
         <v>0.105</v>
       </c>
       <c r="G39">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H39">
         <v>1485.0000000000002</v>
@@ -12422,7 +12422,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G40">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H40">
         <v>1485.0000000000002</v>
@@ -12475,7 +12475,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="G41">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H41">
         <v>1485.0000000000002</v>
@@ -12528,7 +12528,7 @@
         <v>4.6799999999999994E-2</v>
       </c>
       <c r="G42">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H42">
         <v>1485.0000000000005</v>
@@ -12581,7 +12581,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G43">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H43">
         <v>1485.0000000000002</v>
@@ -12634,7 +12634,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G44">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H44">
         <v>1485.0000000000002</v>
@@ -12687,7 +12687,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G45">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H45">
         <v>1485.0000000000002</v>
@@ -12740,7 +12740,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G46">
-        <v>0.55620000000000014</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H46">
         <v>1485.0000000000002</v>
@@ -12793,7 +12793,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G47">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H47">
         <v>1485.0000000000002</v>
@@ -12846,7 +12846,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="G48">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H48">
         <v>1100</v>
@@ -12899,7 +12899,7 @@
         <v>0.373</v>
       </c>
       <c r="G49">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H49">
         <v>1100</v>
@@ -12952,7 +12952,7 @@
         <v>0.82099999999999995</v>
       </c>
       <c r="G50">
-        <v>0.59739999999999993</v>
+        <v>0.44804999999999995</v>
       </c>
       <c r="H50">
         <v>1100</v>
@@ -13005,7 +13005,7 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="G51">
-        <v>0.56135000000000002</v>
+        <v>0.42101249999999996</v>
       </c>
       <c r="H51">
         <v>1100</v>
@@ -13058,7 +13058,7 @@
         <v>0.38919999999999999</v>
       </c>
       <c r="G52">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H52">
         <v>1100</v>
@@ -13111,7 +13111,7 @@
         <v>0.37319999999999998</v>
       </c>
       <c r="G53">
-        <v>0.56135000000000002</v>
+        <v>0.42101249999999996</v>
       </c>
       <c r="H53">
         <v>1100</v>
@@ -13164,7 +13164,7 @@
         <v>0.82299999999999995</v>
       </c>
       <c r="G54">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H54">
         <v>1100</v>
@@ -13217,7 +13217,7 @@
         <v>0.39460000000000001</v>
       </c>
       <c r="G55">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H55">
         <v>1100</v>
@@ -13270,7 +13270,7 @@
         <v>0.39</v>
       </c>
       <c r="G56">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H56">
         <v>1100</v>
@@ -13323,7 +13323,7 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="G57">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H57">
         <v>1100</v>
@@ -13376,7 +13376,7 @@
         <v>0.78500000000000003</v>
       </c>
       <c r="G58">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H58">
         <v>1100</v>
@@ -13429,7 +13429,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G59">
-        <v>0.49440000000000001</v>
+        <v>0.37080000000000007</v>
       </c>
       <c r="H59">
         <v>1485.0000000000002</v>
@@ -13482,7 +13482,7 @@
         <v>0.41199999999999998</v>
       </c>
       <c r="G60">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H60">
         <v>1100</v>
@@ -13535,7 +13535,7 @@
         <v>0.4</v>
       </c>
       <c r="G61">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H61">
         <v>1100</v>
@@ -13588,7 +13588,7 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="G62">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H62">
         <v>1100</v>
@@ -13641,7 +13641,7 @@
         <v>0.3926</v>
       </c>
       <c r="G63">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H63">
         <v>1100</v>
@@ -13694,7 +13694,7 @@
         <v>0.38789999999999997</v>
       </c>
       <c r="G64">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H64">
         <v>1100</v>
@@ -13747,7 +13747,7 @@
         <v>0.41820000000000002</v>
       </c>
       <c r="G65">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H65">
         <v>1100</v>
@@ -13800,7 +13800,7 @@
         <v>0.4178</v>
       </c>
       <c r="G66">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H66">
         <v>1100</v>
@@ -13853,7 +13853,7 @@
         <v>0.41270000000000001</v>
       </c>
       <c r="G67">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H67">
         <v>1100</v>
@@ -13906,7 +13906,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G68">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H68">
         <v>1265</v>
@@ -13959,7 +13959,7 @@
         <v>0.4249</v>
       </c>
       <c r="G69">
-        <v>0.56135000000000002</v>
+        <v>0.42101249999999996</v>
       </c>
       <c r="H69">
         <v>1100</v>
@@ -14012,7 +14012,7 @@
         <v>0.37889999999999996</v>
       </c>
       <c r="G70">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H70">
         <v>1100</v>
@@ -14065,7 +14065,7 @@
         <v>0.41839999999999999</v>
       </c>
       <c r="G71">
-        <v>0.56135000000000002</v>
+        <v>0.42101249999999996</v>
       </c>
       <c r="H71">
         <v>1100</v>
@@ -14118,7 +14118,7 @@
         <v>0.78200000000000003</v>
       </c>
       <c r="G72">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H72">
         <v>1100</v>
@@ -14171,7 +14171,7 @@
         <v>0.85799999999999998</v>
       </c>
       <c r="G73">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H73">
         <v>1100</v>
@@ -14224,7 +14224,7 @@
         <v>0.8</v>
       </c>
       <c r="G74">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H74">
         <v>1100</v>
@@ -14277,7 +14277,7 @@
         <v>0.39100000000000001</v>
       </c>
       <c r="G75">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H75">
         <v>1100</v>
@@ -14330,7 +14330,7 @@
         <v>0.05</v>
       </c>
       <c r="G76">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H76">
         <v>1485.0000000000002</v>
@@ -14383,7 +14383,7 @@
         <v>0.40260000000000001</v>
       </c>
       <c r="G77">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H77">
         <v>1100</v>
@@ -14436,7 +14436,7 @@
         <v>0.40139999999999998</v>
       </c>
       <c r="G78">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H78">
         <v>1100</v>
@@ -14489,7 +14489,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G79">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H79">
         <v>1100</v>
@@ -14542,7 +14542,7 @@
         <v>0.80400000000000005</v>
       </c>
       <c r="G80">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -14595,7 +14595,7 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="G81">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H81">
         <v>1100</v>
@@ -14648,7 +14648,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G82">
-        <v>0.51500000000000001</v>
+        <v>0.38625000000000004</v>
       </c>
       <c r="H82">
         <v>1485.0000000000002</v>
@@ -14701,7 +14701,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G83">
-        <v>0.49440000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H83">
         <v>1485.0000000000002</v>
@@ -14754,7 +14754,7 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="G84">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H84">
         <v>1100</v>
@@ -14807,7 +14807,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G85">
-        <v>0.49440000000000001</v>
+        <v>0.37080000000000007</v>
       </c>
       <c r="H85">
         <v>1485.0000000000002</v>
@@ -14860,7 +14860,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G86">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H86">
         <v>1485.0000000000002</v>
@@ -14913,7 +14913,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G87">
-        <v>0.49439999999999995</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H87">
         <v>1485.0000000000002</v>
@@ -14966,7 +14966,7 @@
         <v>0.38669999999999999</v>
       </c>
       <c r="G88">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H88">
         <v>1100</v>
@@ -15019,7 +15019,7 @@
         <v>0.3891</v>
       </c>
       <c r="G89">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H89">
         <v>1100</v>
@@ -15072,7 +15072,7 @@
         <v>0.39100000000000001</v>
       </c>
       <c r="G90">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H90">
         <v>1100</v>
@@ -15125,7 +15125,7 @@
         <v>0.42010000000000003</v>
       </c>
       <c r="G91">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H91">
         <v>1100</v>
@@ -15178,7 +15178,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="G92">
-        <v>0.56135000000000002</v>
+        <v>0.42101249999999996</v>
       </c>
       <c r="H92">
         <v>1100</v>
@@ -15231,7 +15231,7 @@
         <v>0.43480000000000002</v>
       </c>
       <c r="G93">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H93">
         <v>1100</v>
@@ -15284,7 +15284,7 @@
         <v>0.43139999999999995</v>
       </c>
       <c r="G94">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H94">
         <v>1100</v>
@@ -15337,7 +15337,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="G95">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H95">
         <v>1265</v>
@@ -15390,7 +15390,7 @@
         <v>0.39100000000000001</v>
       </c>
       <c r="G96">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H96">
         <v>1100</v>
@@ -15443,7 +15443,7 @@
         <v>0.40970000000000001</v>
       </c>
       <c r="G97">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H97">
         <v>1100</v>
@@ -15496,7 +15496,7 @@
         <v>0.4118</v>
       </c>
       <c r="G98">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H98">
         <v>1100</v>
@@ -15549,7 +15549,7 @@
         <v>0.41060000000000002</v>
       </c>
       <c r="G99">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H99">
         <v>1100</v>
@@ -15602,7 +15602,7 @@
         <v>0.39</v>
       </c>
       <c r="G100">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H100">
         <v>1100</v>
@@ -15655,7 +15655,7 @@
         <v>0.40200000000000002</v>
       </c>
       <c r="G101">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H101">
         <v>1100</v>
@@ -15708,7 +15708,7 @@
         <v>0.39600000000000002</v>
       </c>
       <c r="G102">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000007</v>
       </c>
       <c r="H102">
         <v>1100</v>
@@ -15761,7 +15761,7 @@
         <v>0.04</v>
       </c>
       <c r="G103">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H103">
         <v>1485.0000000000002</v>
@@ -15814,7 +15814,7 @@
         <v>0.42599999999999999</v>
       </c>
       <c r="G104">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H104">
         <v>1100</v>
@@ -15867,7 +15867,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="G105">
-        <v>0.59739999999999993</v>
+        <v>0.44804999999999995</v>
       </c>
       <c r="H105">
         <v>1100</v>
@@ -15920,7 +15920,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G106">
-        <v>0.56135000000000002</v>
+        <v>0.42101250000000001</v>
       </c>
       <c r="H106">
         <v>1100</v>
@@ -15973,7 +15973,7 @@
         <v>0.04</v>
       </c>
       <c r="G107">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H107">
         <v>1485.0000000000002</v>
@@ -16026,7 +16026,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G108">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H108">
         <v>1265</v>
@@ -16079,7 +16079,7 @@
         <v>0.22600000000000001</v>
       </c>
       <c r="G109">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H109">
         <v>1265</v>
@@ -16132,7 +16132,7 @@
         <v>0.23</v>
       </c>
       <c r="G110">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000011</v>
       </c>
       <c r="H110">
         <v>1265</v>
@@ -16185,7 +16185,7 @@
         <v>0.23</v>
       </c>
       <c r="G111">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000011</v>
       </c>
       <c r="H111">
         <v>1265</v>
@@ -16238,7 +16238,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G112">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H112">
         <v>1485.0000000000002</v>
@@ -16291,7 +16291,7 @@
         <v>0.05</v>
       </c>
       <c r="G113">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H113">
         <v>1485.0000000000002</v>
@@ -16344,7 +16344,7 @@
         <v>0.05</v>
       </c>
       <c r="G114">
-        <v>0.49439999999999995</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="H114">
         <v>1485.0000000000002</v>
@@ -16397,7 +16397,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G115">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000002</v>
       </c>
       <c r="H115">
         <v>1485.0000000000002</v>
@@ -16450,7 +16450,7 @@
         <v>0.05</v>
       </c>
       <c r="G116">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H116">
         <v>1485.0000000000002</v>
@@ -16503,7 +16503,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G117">
-        <v>0.55620000000000003</v>
+        <v>0.41715000000000008</v>
       </c>
       <c r="H117">
         <v>1485.0000000000002</v>
@@ -16556,7 +16556,7 @@
         <v>0.05</v>
       </c>
       <c r="G118">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H118">
         <v>1485.0000000000002</v>
@@ -16609,7 +16609,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="G119">
-        <v>0.53560000000000008</v>
+        <v>0.40170000000000006</v>
       </c>
       <c r="H119">
         <v>1265</v>
@@ -16662,7 +16662,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="G120">
-        <v>0.24719999999999998</v>
+        <v>0.18540000000000001</v>
       </c>
       <c r="H120">
         <v>1188</v>
@@ -16715,7 +16715,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="G121">
-        <v>0.24719999999999998</v>
+        <v>0.18540000000000001</v>
       </c>
       <c r="H121">
         <v>1188</v>
@@ -16768,7 +16768,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G122">
-        <v>0.26264999999999999</v>
+        <v>0.19698750000000001</v>
       </c>
       <c r="H122">
         <v>1188</v>
@@ -16821,7 +16821,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G123">
-        <v>0.28840000000000005</v>
+        <v>0.21630000000000005</v>
       </c>
       <c r="H123">
         <v>1188</v>
@@ -16874,7 +16874,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G124">
-        <v>0.31930000000000003</v>
+        <v>0.23947500000000002</v>
       </c>
       <c r="H124">
         <v>1012</v>
@@ -16927,7 +16927,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G125">
-        <v>0.309</v>
+        <v>0.23175000000000004</v>
       </c>
       <c r="H125">
         <v>1188</v>
@@ -16980,7 +16980,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G126">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H126">
         <v>1188</v>
@@ -17033,7 +17033,7 @@
         <v>0.05</v>
       </c>
       <c r="G127">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H127">
         <v>1188</v>
@@ -17086,7 +17086,7 @@
         <v>0.05</v>
       </c>
       <c r="G128">
-        <v>0.28840000000000005</v>
+        <v>0.21630000000000005</v>
       </c>
       <c r="H128">
         <v>1188</v>
@@ -17139,7 +17139,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G129">
-        <v>0.3296</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H129">
         <v>1782.0000000000002</v>
@@ -22280,7 +22280,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G226">
-        <v>0.49439999999999995</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H226">
         <v>1391.5</v>
@@ -22333,7 +22333,7 @@
         <v>0.08</v>
       </c>
       <c r="G227">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H227">
         <v>1391.5</v>
@@ -22386,7 +22386,7 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="G228">
-        <v>0.42230000000000001</v>
+        <v>0.31672500000000003</v>
       </c>
       <c r="H228">
         <v>1391.5</v>
@@ -22439,7 +22439,7 @@
         <v>0.22600000000000001</v>
       </c>
       <c r="G229">
-        <v>0.42230000000000001</v>
+        <v>0.31672500000000003</v>
       </c>
       <c r="H229">
         <v>1391.5</v>
@@ -22492,7 +22492,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G230">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H230">
         <v>1391.5</v>
@@ -22545,7 +22545,7 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="G231">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H231">
         <v>1391.5</v>
@@ -22598,7 +22598,7 @@
         <v>0.22600000000000001</v>
       </c>
       <c r="G232">
-        <v>0.51500000000000001</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="H232">
         <v>1391.5</v>
@@ -22651,7 +22651,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G233">
-        <v>0.2369</v>
+        <v>0.17767500000000003</v>
       </c>
       <c r="H233">
         <v>1336.5</v>
@@ -22704,7 +22704,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G234">
-        <v>0.2369</v>
+        <v>0.17767500000000003</v>
       </c>
       <c r="H234">
         <v>1336.5</v>
@@ -22757,7 +22757,7 @@
         <v>0.15</v>
       </c>
       <c r="G235">
-        <v>0.23690000000000003</v>
+        <v>0.17767500000000003</v>
       </c>
       <c r="H235">
         <v>1336.5</v>
@@ -22810,7 +22810,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G236">
-        <v>0.23690000000000005</v>
+        <v>0.17767500000000003</v>
       </c>
       <c r="H236">
         <v>1336.5</v>
@@ -22863,7 +22863,7 @@
         <v>0.14050000000000001</v>
       </c>
       <c r="G237">
-        <v>0.25235000000000002</v>
+        <v>0.1892625</v>
       </c>
       <c r="H237">
         <v>1336.5</v>
@@ -22916,7 +22916,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="G238">
-        <v>0.25235000000000002</v>
+        <v>0.1892625</v>
       </c>
       <c r="H238">
         <v>1336.5</v>
@@ -22969,7 +22969,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G239">
-        <v>0.25235000000000002</v>
+        <v>0.1892625</v>
       </c>
       <c r="H239">
         <v>1336.5</v>
@@ -23022,7 +23022,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G240">
-        <v>0.25235000000000002</v>
+        <v>0.1892625</v>
       </c>
       <c r="H240">
         <v>1336.5</v>
@@ -23075,7 +23075,7 @@
         <v>0.05</v>
       </c>
       <c r="G241">
-        <v>0.27810000000000001</v>
+        <v>0.20857500000000001</v>
       </c>
       <c r="H241">
         <v>1336.5</v>
@@ -23128,7 +23128,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G242">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H242">
         <v>1138.5</v>
@@ -23181,7 +23181,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G243">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H243">
         <v>1138.5</v>
@@ -23234,7 +23234,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G244">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H244">
         <v>1138.5</v>
@@ -23287,7 +23287,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G245">
-        <v>0.25235000000000002</v>
+        <v>0.1892625</v>
       </c>
       <c r="H245">
         <v>1336.5</v>
@@ -23340,7 +23340,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G246">
-        <v>0.27810000000000001</v>
+        <v>0.20857500000000004</v>
       </c>
       <c r="H246">
         <v>1336.5</v>
@@ -23393,7 +23393,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G247">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H247">
         <v>1138.5</v>
@@ -23446,7 +23446,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G248">
-        <v>0.26264999999999999</v>
+        <v>0.19698749999999998</v>
       </c>
       <c r="H248">
         <v>1138.5</v>
@@ -23499,7 +23499,7 @@
         <v>0.05</v>
       </c>
       <c r="G249">
-        <v>0.27810000000000001</v>
+        <v>0.20857500000000001</v>
       </c>
       <c r="H249">
         <v>1336.5</v>
@@ -23552,7 +23552,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G250">
-        <v>0.31414999999999998</v>
+        <v>0.23561250000000003</v>
       </c>
       <c r="H250">
         <v>1485.0000000000002</v>
@@ -23605,7 +23605,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G251">
-        <v>0.32445000000000002</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="H251">
         <v>1485.0000000000002</v>
@@ -23658,7 +23658,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G252">
-        <v>0.32445000000000002</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="H252">
         <v>1485.0000000000002</v>
@@ -23711,7 +23711,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G253">
-        <v>0.32445000000000002</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="H253">
         <v>1485.0000000000002</v>
@@ -23764,7 +23764,7 @@
         <v>0.06</v>
       </c>
       <c r="G254">
-        <v>0.32445000000000002</v>
+        <v>0.24333750000000004</v>
       </c>
       <c r="H254">
         <v>1485.0000000000002</v>
@@ -23817,7 +23817,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G255">
-        <v>0.33475000000000005</v>
+        <v>0.25106250000000002</v>
       </c>
       <c r="H255">
         <v>1485.0000000000002</v>
@@ -23870,7 +23870,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G256">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H256">
         <v>1485.0000000000002</v>
@@ -23923,7 +23923,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G257">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H257">
         <v>1485.0000000000002</v>
@@ -23976,7 +23976,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G258">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H258">
         <v>1485.0000000000002</v>
@@ -24029,7 +24029,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G259">
-        <v>0.36049999999999999</v>
+        <v>0.27037499999999998</v>
       </c>
       <c r="H259">
         <v>1265</v>
@@ -24082,7 +24082,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G260">
-        <v>0.33475000000000005</v>
+        <v>0.25106250000000002</v>
       </c>
       <c r="H260">
         <v>1485.0000000000002</v>
@@ -24135,7 +24135,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G261">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H261">
         <v>1265</v>
@@ -24188,7 +24188,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G262">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H262">
         <v>1265</v>
@@ -24241,7 +24241,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G263">
-        <v>0.32445000000000002</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="H263">
         <v>1485.0000000000002</v>
@@ -24294,7 +24294,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G264">
-        <v>0.33475000000000005</v>
+        <v>0.25106250000000002</v>
       </c>
       <c r="H264">
         <v>1485.0000000000002</v>
@@ -24347,7 +24347,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="G265">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H265">
         <v>1265</v>
@@ -24400,7 +24400,7 @@
         <v>7.3599999999999999E-2</v>
       </c>
       <c r="G266">
-        <v>0.35020000000000001</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H266">
         <v>1265</v>
@@ -24453,7 +24453,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G267">
-        <v>0.29869999999999997</v>
+        <v>0.22402499999999997</v>
       </c>
       <c r="H267">
         <v>1930.5000000000005</v>
@@ -24506,7 +24506,7 @@
         <v>0.05</v>
       </c>
       <c r="G268">
-        <v>0.309</v>
+        <v>0.23175000000000001</v>
       </c>
       <c r="H268">
         <v>1930.5000000000007</v>
@@ -24559,7 +24559,7 @@
         <v>0.04</v>
       </c>
       <c r="G269">
-        <v>0.29869999999999997</v>
+        <v>0.22402499999999997</v>
       </c>
       <c r="H269">
         <v>1930.5000000000005</v>
@@ -24612,7 +24612,7 @@
         <v>0.04</v>
       </c>
       <c r="G270">
-        <v>0.29869999999999997</v>
+        <v>0.22402499999999997</v>
       </c>
       <c r="H270">
         <v>1930.5000000000005</v>
@@ -24644,7 +24644,7 @@
         <v>0.08</v>
       </c>
       <c r="G271">
-        <v>0.3296</v>
+        <v>0.2472</v>
       </c>
       <c r="H271">
         <v>1644.4999999999995</v>
@@ -24676,7 +24676,7 @@
         <v>0.08</v>
       </c>
       <c r="G272">
-        <v>0.3296</v>
+        <v>0.2472</v>
       </c>
       <c r="H272">
         <v>1644.4999999999995</v>
@@ -24708,7 +24708,7 @@
         <v>0.04</v>
       </c>
       <c r="G273">
-        <v>0.309</v>
+        <v>0.23174999999999998</v>
       </c>
       <c r="H273">
         <v>1930.5000000000005</v>
@@ -24740,7 +24740,7 @@
         <v>0.04</v>
       </c>
       <c r="G274">
-        <v>0.29869999999999997</v>
+        <v>0.22402499999999997</v>
       </c>
       <c r="H274">
         <v>1930.5000000000005</v>
@@ -24772,7 +24772,7 @@
         <v>0.08</v>
       </c>
       <c r="G275">
-        <v>0.3296</v>
+        <v>0.2472</v>
       </c>
       <c r="H275">
         <v>1644.4999999999995</v>
@@ -24804,7 +24804,7 @@
         <v>0.08</v>
       </c>
       <c r="G276">
-        <v>0.3296</v>
+        <v>0.2472</v>
       </c>
       <c r="H276">
         <v>1644.4999999999995</v>

--- a/VerveStacks_ESP/vt_vervestacks_ESP_v1.xlsx
+++ b/VerveStacks_ESP/vt_vervestacks_ESP_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{759E3DAF-536D-4A17-A4C9-BAD9CCA716FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE25881-6EDD-4A5D-8A16-1068D076F013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B0B896D4-49D1-4B2A-B113-C78CF397E43E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FD7979AC-F0C0-4F26-B10F-0CFC0C60D078}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2774,7 +2774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC80FF62-5FAD-4B75-A264-97223D3FF4D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAC6FDA-BDAE-4BCC-A67F-1C6393ECBD53}">
   <dimension ref="B9:T164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10800,7 +10800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787129DC-07FC-418D-8423-A8D8FF72ADFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA615750-0F5E-4D16-817D-9C7B60B962FC}">
   <dimension ref="B9:T372"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24851,7 +24851,7 @@
         <v>33</v>
       </c>
       <c r="L277">
-        <v>0.23722126823254083</v>
+        <v>0.23722126823254081</v>
       </c>
     </row>
     <row r="278" spans="2:12" x14ac:dyDescent="0.45">
@@ -26892,7 +26892,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L336">
-        <v>0.29545740903940854</v>
+        <v>0.29545740903940859</v>
       </c>
     </row>
     <row r="337" spans="2:12" x14ac:dyDescent="0.45">
